--- a/respostas_anonimizadas_perfil1.xlsx
+++ b/respostas_anonimizadas_perfil1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jose_\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{260DC4D1-D27B-44C2-BA87-6EF471316241}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17DE10F-7BDC-4B2C-9C21-A57F2742B283}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="945" windowWidth="29040" windowHeight="15720" xr2:uid="{97D89DCA-D951-4D4B-9F83-3E33AFBDA3F8}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Avaliação_de_Aceitação_de_Tecnologia_Submissions_2026_10_14" localSheetId="0">Planilha1!$A$1:$AE$32</definedName>
+    <definedName name="Avaliação_de_Aceitação_de_Tecnologia_Submissions_2026_10_14" localSheetId="0">Planilha1!$A$1:$AE$28</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="199">
   <si>
     <t>Qual é o seu nível de formação atual?</t>
   </si>
@@ -675,84 +675,6 @@
   </si>
   <si>
     <t xml:space="preserve">achei que funcionou bem nas para as quais demandas que eu utilizei </t>
-  </si>
-  <si>
-    <t>8º Período</t>
-  </si>
-  <si>
-    <t>não tive</t>
-  </si>
-  <si>
-    <t>experiência com outros chatbots</t>
-  </si>
-  <si>
-    <t>na economia de tempo, pois em muitos prontuários eletrônicos há diversas informações repetidas, as quais o médico acaba perdendo tempo as lendo novamente em cada registro de consulta. Com a integração, o chatbot consegue explicar exatamente o que é importante para o momento atual</t>
-  </si>
-  <si>
-    <t>eu poderia confiar na maioria das situações, caso soubesse de estudos que mostrassem que esta IA gera poucas alucinações e envia informações corretas na maioria das vezes</t>
-  </si>
-  <si>
-    <t>colocar uma referência na frente de cada informação, em forma de número clicável e direcionável ao prontuário ou à fonte de onde aquela informação foi retirada</t>
-  </si>
-  <si>
-    <t>eu pedi para ele falar sobre a paciente, e ele só me deu os dados. Eu esperava que fosse me explicar o motivo do acompanhamento, etc</t>
-  </si>
-  <si>
-    <t>3 a 5 anos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ausência de prática </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Interatividade </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deixou tudo mais intuitivo </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confiaria: atendimentos básicos / não confiaria: atendimentos com tópicos sensíveis </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integração </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não tenho oq falar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">O layout para smartphones, tendo em vista que apresentou um bug ao fechar o teclado em que a tela ainda continua dividida, dificultando a visualização da conversa </t>
-  </si>
-  <si>
-    <t xml:space="preserve">A rapidez das respostas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garantindo que as informações eram fidedignas </t>
-  </si>
-  <si>
-    <t>Confiaria durante uma consulta clínica. Não confiaria durante atendimentos de emergência pois não haveria tempo para consultar informações.</t>
-  </si>
-  <si>
-    <t>O layout para smartphones, pelo bug apresentado.</t>
-  </si>
-  <si>
-    <t>Bug no layout em celulares.</t>
-  </si>
-  <si>
-    <t>A ausência de mais informações clínicas e acesso a mais exames, já que a ferramente está em processo inicial.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Design amigável para o usuário. </t>
-  </si>
-  <si>
-    <t>Ele recupera informações de prontuários e realiza resumos clínicos e responde de forma aplicada à pergunta.</t>
-  </si>
-  <si>
-    <t>Confiaria: recuperar dados clínicos com base no prontuário; não confiaria de fato: tomar condutas totalmente com base nas indicações do bot.</t>
-  </si>
-  <si>
-    <t>Banco de informações mais refinado e alinhado com diretrizes brasileiras, mas apresentando a opção de diretrizes internacionais.</t>
-  </si>
-  <si>
-    <t>O sistema não recuperou a informação do último atendimento da paciente Maria Fernanda.</t>
   </si>
 </sst>
 </file>
@@ -1108,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6275DD6A-A0F6-40CA-9859-9D3925A7AFB5}">
-  <dimension ref="A1:AE32"/>
+  <dimension ref="A1:AE28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.7109375" bestFit="1" customWidth="1"/>
@@ -3782,386 +3704,6 @@
         <v>198</v>
       </c>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" t="s">
-        <v>199</v>
-      </c>
-      <c r="C29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29">
-        <v>5</v>
-      </c>
-      <c r="G29">
-        <v>5</v>
-      </c>
-      <c r="H29">
-        <v>4</v>
-      </c>
-      <c r="I29">
-        <v>4</v>
-      </c>
-      <c r="J29">
-        <v>3</v>
-      </c>
-      <c r="K29">
-        <v>5</v>
-      </c>
-      <c r="L29">
-        <v>5</v>
-      </c>
-      <c r="M29">
-        <v>4</v>
-      </c>
-      <c r="N29">
-        <v>4</v>
-      </c>
-      <c r="O29">
-        <v>3</v>
-      </c>
-      <c r="P29">
-        <v>3</v>
-      </c>
-      <c r="Q29">
-        <v>5</v>
-      </c>
-      <c r="R29">
-        <v>5</v>
-      </c>
-      <c r="S29">
-        <v>4</v>
-      </c>
-      <c r="T29">
-        <v>5</v>
-      </c>
-      <c r="U29">
-        <v>4</v>
-      </c>
-      <c r="V29">
-        <v>5</v>
-      </c>
-      <c r="W29">
-        <v>4</v>
-      </c>
-      <c r="X29">
-        <v>5</v>
-      </c>
-      <c r="Y29">
-        <v>5</v>
-      </c>
-      <c r="Z29" t="s">
-        <v>200</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>201</v>
-      </c>
-      <c r="AB29" t="s">
-        <v>202</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>203</v>
-      </c>
-      <c r="AD29" t="s">
-        <v>204</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" t="s">
-        <v>206</v>
-      </c>
-      <c r="D30" t="s">
-        <v>49</v>
-      </c>
-      <c r="E30" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30">
-        <v>7</v>
-      </c>
-      <c r="G30">
-        <v>7</v>
-      </c>
-      <c r="H30">
-        <v>5</v>
-      </c>
-      <c r="I30">
-        <v>5</v>
-      </c>
-      <c r="J30">
-        <v>5</v>
-      </c>
-      <c r="K30">
-        <v>5</v>
-      </c>
-      <c r="L30">
-        <v>4</v>
-      </c>
-      <c r="M30">
-        <v>5</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>5</v>
-      </c>
-      <c r="P30">
-        <v>5</v>
-      </c>
-      <c r="Q30">
-        <v>3</v>
-      </c>
-      <c r="R30">
-        <v>5</v>
-      </c>
-      <c r="S30">
-        <v>5</v>
-      </c>
-      <c r="T30">
-        <v>5</v>
-      </c>
-      <c r="U30">
-        <v>5</v>
-      </c>
-      <c r="V30">
-        <v>5</v>
-      </c>
-      <c r="W30">
-        <v>5</v>
-      </c>
-      <c r="X30">
-        <v>3</v>
-      </c>
-      <c r="Y30">
-        <v>5</v>
-      </c>
-      <c r="Z30" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA30" t="s">
-        <v>208</v>
-      </c>
-      <c r="AB30" t="s">
-        <v>209</v>
-      </c>
-      <c r="AC30" t="s">
-        <v>210</v>
-      </c>
-      <c r="AD30" t="s">
-        <v>211</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>31</v>
-      </c>
-      <c r="B31" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" t="s">
-        <v>35</v>
-      </c>
-      <c r="F31">
-        <v>5</v>
-      </c>
-      <c r="G31">
-        <v>2</v>
-      </c>
-      <c r="H31">
-        <v>5</v>
-      </c>
-      <c r="I31">
-        <v>5</v>
-      </c>
-      <c r="J31">
-        <v>5</v>
-      </c>
-      <c r="K31">
-        <v>5</v>
-      </c>
-      <c r="L31">
-        <v>5</v>
-      </c>
-      <c r="M31">
-        <v>5</v>
-      </c>
-      <c r="N31">
-        <v>5</v>
-      </c>
-      <c r="O31">
-        <v>5</v>
-      </c>
-      <c r="P31">
-        <v>5</v>
-      </c>
-      <c r="Q31">
-        <v>5</v>
-      </c>
-      <c r="R31">
-        <v>4</v>
-      </c>
-      <c r="S31">
-        <v>5</v>
-      </c>
-      <c r="T31">
-        <v>5</v>
-      </c>
-      <c r="U31">
-        <v>5</v>
-      </c>
-      <c r="V31">
-        <v>5</v>
-      </c>
-      <c r="W31">
-        <v>5</v>
-      </c>
-      <c r="X31">
-        <v>5</v>
-      </c>
-      <c r="Y31">
-        <v>5</v>
-      </c>
-      <c r="Z31" t="s">
-        <v>213</v>
-      </c>
-      <c r="AA31" t="s">
-        <v>214</v>
-      </c>
-      <c r="AB31" t="s">
-        <v>215</v>
-      </c>
-      <c r="AC31" t="s">
-        <v>216</v>
-      </c>
-      <c r="AD31" t="s">
-        <v>217</v>
-      </c>
-      <c r="AE31" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>199</v>
-      </c>
-      <c r="C32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32" t="s">
-        <v>49</v>
-      </c>
-      <c r="E32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32">
-        <v>7</v>
-      </c>
-      <c r="G32">
-        <v>7</v>
-      </c>
-      <c r="H32">
-        <v>5</v>
-      </c>
-      <c r="I32">
-        <v>5</v>
-      </c>
-      <c r="J32">
-        <v>5</v>
-      </c>
-      <c r="K32">
-        <v>5</v>
-      </c>
-      <c r="L32">
-        <v>5</v>
-      </c>
-      <c r="M32">
-        <v>4</v>
-      </c>
-      <c r="N32">
-        <v>4</v>
-      </c>
-      <c r="O32">
-        <v>5</v>
-      </c>
-      <c r="P32">
-        <v>5</v>
-      </c>
-      <c r="Q32">
-        <v>5</v>
-      </c>
-      <c r="R32">
-        <v>5</v>
-      </c>
-      <c r="S32">
-        <v>4</v>
-      </c>
-      <c r="T32">
-        <v>5</v>
-      </c>
-      <c r="U32">
-        <v>5</v>
-      </c>
-      <c r="V32">
-        <v>5</v>
-      </c>
-      <c r="W32">
-        <v>3</v>
-      </c>
-      <c r="X32">
-        <v>5</v>
-      </c>
-      <c r="Y32">
-        <v>5</v>
-      </c>
-      <c r="Z32" t="s">
-        <v>219</v>
-      </c>
-      <c r="AA32" t="s">
-        <v>220</v>
-      </c>
-      <c r="AB32" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC32" t="s">
-        <v>222</v>
-      </c>
-      <c r="AD32" t="s">
-        <v>223</v>
-      </c>
-      <c r="AE32" t="s">
-        <v>224</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
